--- a/data/stock/dividends.xlsx
+++ b/data/stock/dividends.xlsx
@@ -71,211 +71,211 @@
     <t>招商银行A</t>
   </si>
   <si>
-    <t>sh600036</t>
+    <t>600036</t>
   </si>
   <si>
     <t>海尔智家</t>
   </si>
   <si>
-    <t>sh600690</t>
+    <t>600690</t>
   </si>
   <si>
     <t>长江电力</t>
   </si>
   <si>
-    <t>sh600900</t>
+    <t>600900</t>
   </si>
   <si>
     <t>中国移动A</t>
   </si>
   <si>
-    <t>sh600941</t>
+    <t>600941</t>
   </si>
   <si>
     <t>美的集团</t>
   </si>
   <si>
-    <t>sz000333</t>
+    <t>000333</t>
   </si>
   <si>
     <t>格力电器</t>
   </si>
   <si>
-    <t>sz000651</t>
+    <t>000651</t>
   </si>
   <si>
     <t>农业银行</t>
   </si>
   <si>
-    <t>sh601288</t>
+    <t>601288</t>
   </si>
   <si>
     <t>国投电力</t>
   </si>
   <si>
-    <t>sh600886</t>
+    <t>600886</t>
   </si>
   <si>
     <t>中国平安A</t>
   </si>
   <si>
-    <t>sh601318</t>
+    <t>601318</t>
   </si>
   <si>
     <t>中远海控A</t>
   </si>
   <si>
-    <t>sh601919</t>
+    <t>601919</t>
   </si>
   <si>
     <t>伊利股份</t>
   </si>
   <si>
-    <t>sh600887</t>
+    <t>600887</t>
   </si>
   <si>
     <t>云南白药</t>
   </si>
   <si>
-    <t>sz000538</t>
+    <t>000538</t>
   </si>
   <si>
     <t>贵州茅台</t>
   </si>
   <si>
-    <t>sh600519</t>
+    <t>600519</t>
   </si>
   <si>
     <t>泸州老窖</t>
   </si>
   <si>
-    <t>sz000568</t>
+    <t>000568</t>
   </si>
   <si>
     <t>中国太保</t>
   </si>
   <si>
-    <t>sh601601</t>
+    <t>601601</t>
   </si>
   <si>
     <t>宁波银行</t>
   </si>
   <si>
-    <t>sz002142</t>
+    <t>002142</t>
   </si>
   <si>
     <t>中国海油</t>
   </si>
   <si>
-    <t>sh600938</t>
+    <t>600938</t>
   </si>
   <si>
     <t>中国神华</t>
   </si>
   <si>
-    <t>sh601088</t>
+    <t>601088</t>
   </si>
   <si>
     <t>万华化学</t>
   </si>
   <si>
-    <t>sh600309</t>
+    <t>600309</t>
   </si>
   <si>
     <t>五粮液</t>
   </si>
   <si>
-    <t>sz000858</t>
+    <t>000858</t>
   </si>
   <si>
     <t>中信建投</t>
   </si>
   <si>
-    <t>sh601066</t>
+    <t>601066</t>
   </si>
   <si>
     <t>中国石化</t>
   </si>
   <si>
-    <t>sh600028</t>
+    <t>600028</t>
   </si>
   <si>
     <t>云天化</t>
   </si>
   <si>
-    <t>sh600096</t>
+    <t>600096</t>
   </si>
   <si>
     <t>工商银行</t>
   </si>
   <si>
-    <t>sh601398</t>
+    <t>601398</t>
   </si>
   <si>
     <t>中国石油A</t>
   </si>
   <si>
-    <t>sh601857</t>
+    <t>601857</t>
   </si>
   <si>
     <t>青岛啤酒A</t>
   </si>
   <si>
-    <t>sh600600</t>
+    <t>600600</t>
   </si>
   <si>
     <t>中国广核</t>
   </si>
   <si>
-    <t>sz003816</t>
+    <t>003816</t>
   </si>
   <si>
     <t>中国核电</t>
   </si>
   <si>
-    <t>sh601985</t>
+    <t>601985</t>
   </si>
   <si>
     <t>国电电力</t>
   </si>
   <si>
-    <t>sh600795</t>
+    <t>600795</t>
   </si>
   <si>
     <t>华能水电</t>
   </si>
   <si>
-    <t>sh600025</t>
+    <t>600025</t>
   </si>
   <si>
     <t>中国电信A</t>
   </si>
   <si>
-    <t>sh601728</t>
+    <t>601728</t>
   </si>
   <si>
     <t>建设银行A</t>
   </si>
   <si>
-    <t>sh601939</t>
+    <t>601939</t>
   </si>
   <si>
     <t>中国银行</t>
   </si>
   <si>
-    <t>sh601988</t>
+    <t>601988</t>
   </si>
   <si>
     <t>邮储银行</t>
   </si>
   <si>
-    <t>sh601658</t>
+    <t>601658</t>
   </si>
   <si>
     <t>交通银行</t>
   </si>
   <si>
-    <t>sh601328</t>
+    <t>601328</t>
   </si>
   <si>
     <t>中国移动H</t>
@@ -910,6 +910,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1445,6 +1448,9 @@
   <sheetPr/>
   <dimension ref="A1:M286"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="12.1538461538462" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -1491,7 +1497,7 @@
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C2">
@@ -1529,7 +1535,7 @@
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3">
@@ -1567,7 +1573,7 @@
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -1605,7 +1611,7 @@
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5">
@@ -1643,7 +1649,7 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C6">
@@ -1681,7 +1687,7 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C7">
@@ -1719,7 +1725,7 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C8">
@@ -1757,7 +1763,7 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C9">
@@ -1795,7 +1801,7 @@
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10">
@@ -1833,7 +1839,7 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11">
@@ -1871,7 +1877,7 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12">
@@ -1909,7 +1915,7 @@
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13">
@@ -1947,7 +1953,7 @@
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14">
@@ -1985,7 +1991,7 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15">
@@ -2023,7 +2029,7 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16">
@@ -2061,7 +2067,7 @@
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17">
@@ -2099,7 +2105,7 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C18">
@@ -2137,7 +2143,7 @@
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C19">
@@ -2175,7 +2181,7 @@
       <c r="A20" t="s">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C20">
@@ -2213,7 +2219,7 @@
       <c r="A21" t="s">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C21">
@@ -2251,7 +2257,7 @@
       <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C22">
@@ -2289,7 +2295,7 @@
       <c r="A23" t="s">
         <v>17</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C23">
@@ -2327,7 +2333,7 @@
       <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C24">
@@ -2365,7 +2371,7 @@
       <c r="A25" t="s">
         <v>17</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C25">
@@ -2403,7 +2409,7 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C26">
@@ -2441,7 +2447,7 @@
       <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C27">
@@ -2479,7 +2485,7 @@
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C28">
@@ -2517,7 +2523,7 @@
       <c r="A29" t="s">
         <v>19</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29">
@@ -2555,7 +2561,7 @@
       <c r="A30" t="s">
         <v>21</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C30">
@@ -2590,7 +2596,7 @@
       <c r="A31" t="s">
         <v>21</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31">
@@ -2625,7 +2631,7 @@
       <c r="A32" t="s">
         <v>21</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C32">
@@ -2660,7 +2666,7 @@
       <c r="A33" t="s">
         <v>21</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C33">
@@ -2695,7 +2701,7 @@
       <c r="A34" t="s">
         <v>21</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C34">
@@ -2730,7 +2736,7 @@
       <c r="A35" t="s">
         <v>21</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C35">
@@ -2765,7 +2771,7 @@
       <c r="A36" t="s">
         <v>21</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C36">
@@ -2800,7 +2806,7 @@
       <c r="A37" t="s">
         <v>21</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C37">
@@ -2835,7 +2841,7 @@
       <c r="A38" t="s">
         <v>21</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C38">
@@ -2870,7 +2876,7 @@
       <c r="A39" t="s">
         <v>23</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C39">
@@ -2905,7 +2911,7 @@
       <c r="A40" t="s">
         <v>23</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C40">
@@ -2940,7 +2946,7 @@
       <c r="A41" t="s">
         <v>23</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C41">
@@ -2975,7 +2981,7 @@
       <c r="A42" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C42">
@@ -3010,7 +3016,7 @@
       <c r="A43" t="s">
         <v>23</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C43">
@@ -3045,7 +3051,7 @@
       <c r="A44" t="s">
         <v>23</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C44">
@@ -3080,7 +3086,7 @@
       <c r="A45" t="s">
         <v>23</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C45">
@@ -3115,7 +3121,7 @@
       <c r="A46" t="s">
         <v>23</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C46">
@@ -3150,7 +3156,7 @@
       <c r="A47" t="s">
         <v>23</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C47">
@@ -3185,7 +3191,7 @@
       <c r="A48" t="s">
         <v>25</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C48">
@@ -3220,7 +3226,7 @@
       <c r="A49" t="s">
         <v>25</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C49">
@@ -3255,7 +3261,7 @@
       <c r="A50" t="s">
         <v>25</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C50">
@@ -3290,7 +3296,7 @@
       <c r="A51" t="s">
         <v>25</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C51">
@@ -3325,7 +3331,7 @@
       <c r="A52" t="s">
         <v>25</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C52">
@@ -3360,7 +3366,7 @@
       <c r="A53" t="s">
         <v>25</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C53">
@@ -3395,7 +3401,7 @@
       <c r="A54" t="s">
         <v>25</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C54">
@@ -3430,7 +3436,7 @@
       <c r="A55" t="s">
         <v>25</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C55">
@@ -3465,7 +3471,7 @@
       <c r="A56" t="s">
         <v>27</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C56">
@@ -3503,7 +3509,7 @@
       <c r="A57" t="s">
         <v>27</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C57">
@@ -3541,7 +3547,7 @@
       <c r="A58" t="s">
         <v>27</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C58">
@@ -3579,7 +3585,7 @@
       <c r="A59" t="s">
         <v>27</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C59">
@@ -3617,7 +3623,7 @@
       <c r="A60" t="s">
         <v>27</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C60">
@@ -3655,7 +3661,7 @@
       <c r="A61" t="s">
         <v>27</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C61">
@@ -3693,7 +3699,7 @@
       <c r="A62" t="s">
         <v>27</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C62">
@@ -3731,7 +3737,7 @@
       <c r="A63" t="s">
         <v>27</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C63">
@@ -3769,7 +3775,7 @@
       <c r="A64" t="s">
         <v>29</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C64">
@@ -3804,7 +3810,7 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C65">
@@ -3839,7 +3845,7 @@
       <c r="A66" t="s">
         <v>29</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C66">
@@ -3874,7 +3880,7 @@
       <c r="A67" t="s">
         <v>29</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C67">
@@ -3909,7 +3915,7 @@
       <c r="A68" t="s">
         <v>29</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C68">
@@ -3944,7 +3950,7 @@
       <c r="A69" t="s">
         <v>29</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C69">
@@ -3979,7 +3985,7 @@
       <c r="A70" t="s">
         <v>29</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C70">
@@ -4014,7 +4020,7 @@
       <c r="A71" t="s">
         <v>29</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C71">
@@ -4049,7 +4055,7 @@
       <c r="A72" t="s">
         <v>29</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C72">
@@ -4084,7 +4090,7 @@
       <c r="A73" t="s">
         <v>31</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C73">
@@ -4122,7 +4128,7 @@
       <c r="A74" t="s">
         <v>31</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C74">
@@ -4160,7 +4166,7 @@
       <c r="A75" t="s">
         <v>31</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C75">
@@ -4198,7 +4204,7 @@
       <c r="A76" t="s">
         <v>31</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C76">
@@ -4236,7 +4242,7 @@
       <c r="A77" t="s">
         <v>31</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C77">
@@ -4274,7 +4280,7 @@
       <c r="A78" t="s">
         <v>33</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C78">
@@ -4312,7 +4318,7 @@
       <c r="A79" t="s">
         <v>33</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C79">
@@ -4350,7 +4356,7 @@
       <c r="A80" t="s">
         <v>33</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C80">
@@ -4388,7 +4394,7 @@
       <c r="A81" t="s">
         <v>33</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C81">
@@ -4426,7 +4432,7 @@
       <c r="A82" t="s">
         <v>33</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C82">
@@ -4464,7 +4470,7 @@
       <c r="A83" t="s">
         <v>33</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C83">
@@ -4502,7 +4508,7 @@
       <c r="A84" t="s">
         <v>33</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C84">
@@ -4540,7 +4546,7 @@
       <c r="A85" t="s">
         <v>33</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C85">
@@ -4578,7 +4584,7 @@
       <c r="A86" t="s">
         <v>35</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C86">
@@ -4616,7 +4622,7 @@
       <c r="A87" t="s">
         <v>35</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C87">
@@ -4654,7 +4660,7 @@
       <c r="A88" t="s">
         <v>35</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C88">
@@ -4692,7 +4698,7 @@
       <c r="A89" t="s">
         <v>35</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C89">
@@ -4730,7 +4736,7 @@
       <c r="A90" t="s">
         <v>35</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C90">
@@ -4768,7 +4774,7 @@
       <c r="A91" t="s">
         <v>35</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C91">
@@ -4806,7 +4812,7 @@
       <c r="A92" t="s">
         <v>35</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C92">
@@ -4844,7 +4850,7 @@
       <c r="A93" t="s">
         <v>35</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C93">
@@ -4882,7 +4888,7 @@
       <c r="A94" t="s">
         <v>37</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C94">
@@ -4920,7 +4926,7 @@
       <c r="A95" t="s">
         <v>37</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C95">
@@ -4958,7 +4964,7 @@
       <c r="A96" t="s">
         <v>37</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C96">
@@ -4996,7 +5002,7 @@
       <c r="A97" t="s">
         <v>37</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C97">
@@ -5034,7 +5040,7 @@
       <c r="A98" t="s">
         <v>37</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C98">
@@ -5072,7 +5078,7 @@
       <c r="A99" t="s">
         <v>37</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C99">
@@ -5110,7 +5116,7 @@
       <c r="A100" t="s">
         <v>37</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C100">
@@ -5148,7 +5154,7 @@
       <c r="A101" t="s">
         <v>37</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C101">
@@ -5186,7 +5192,7 @@
       <c r="A102" t="s">
         <v>39</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C102">
@@ -5224,7 +5230,7 @@
       <c r="A103" t="s">
         <v>39</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C103">
@@ -5262,7 +5268,7 @@
       <c r="A104" t="s">
         <v>39</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C104">
@@ -5300,7 +5306,7 @@
       <c r="A105" t="s">
         <v>39</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C105">
@@ -5338,7 +5344,7 @@
       <c r="A106" t="s">
         <v>39</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C106">
@@ -5376,7 +5382,7 @@
       <c r="A107" t="s">
         <v>39</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C107">
@@ -5414,7 +5420,7 @@
       <c r="A108" t="s">
         <v>39</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C108">
@@ -5452,7 +5458,7 @@
       <c r="A109" t="s">
         <v>39</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C109">
@@ -5490,7 +5496,7 @@
       <c r="A110" t="s">
         <v>41</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C110">
@@ -5528,7 +5534,7 @@
       <c r="A111" t="s">
         <v>41</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C111">
@@ -5566,7 +5572,7 @@
       <c r="A112" t="s">
         <v>41</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C112">
@@ -5604,7 +5610,7 @@
       <c r="A113" t="s">
         <v>41</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C113">
@@ -5642,7 +5648,7 @@
       <c r="A114" t="s">
         <v>41</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C114">
@@ -5680,7 +5686,7 @@
       <c r="A115" t="s">
         <v>41</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C115">
@@ -5718,7 +5724,7 @@
       <c r="A116" t="s">
         <v>41</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C116">
@@ -5756,7 +5762,7 @@
       <c r="A117" t="s">
         <v>41</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C117">
@@ -5794,7 +5800,7 @@
       <c r="A118" t="s">
         <v>43</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C118">
@@ -5832,7 +5838,7 @@
       <c r="A119" t="s">
         <v>43</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C119">
@@ -5870,7 +5876,7 @@
       <c r="A120" t="s">
         <v>43</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C120">
@@ -5908,7 +5914,7 @@
       <c r="A121" t="s">
         <v>43</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C121">
@@ -5946,7 +5952,7 @@
       <c r="A122" t="s">
         <v>43</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C122">
@@ -5984,7 +5990,7 @@
       <c r="A123" t="s">
         <v>43</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C123">
@@ -6022,7 +6028,7 @@
       <c r="A124" t="s">
         <v>43</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C124">
@@ -6060,7 +6066,7 @@
       <c r="A125" t="s">
         <v>43</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C125">
@@ -6098,7 +6104,7 @@
       <c r="A126" t="s">
         <v>45</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C126">
@@ -6136,7 +6142,7 @@
       <c r="A127" t="s">
         <v>45</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C127">
@@ -6174,7 +6180,7 @@
       <c r="A128" t="s">
         <v>45</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C128">
@@ -6212,7 +6218,7 @@
       <c r="A129" t="s">
         <v>45</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C129">
@@ -6250,7 +6256,7 @@
       <c r="A130" t="s">
         <v>45</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C130">
@@ -6288,7 +6294,7 @@
       <c r="A131" t="s">
         <v>45</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C131">
@@ -6326,7 +6332,7 @@
       <c r="A132" t="s">
         <v>45</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C132">
@@ -6364,7 +6370,7 @@
       <c r="A133" t="s">
         <v>45</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C133">
@@ -6402,7 +6408,7 @@
       <c r="A134" t="s">
         <v>47</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C134">
@@ -6440,7 +6446,7 @@
       <c r="A135" t="s">
         <v>47</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C135">
@@ -6478,7 +6484,7 @@
       <c r="A136" t="s">
         <v>47</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C136">
@@ -6516,7 +6522,7 @@
       <c r="A137" t="s">
         <v>47</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C137">
@@ -6554,7 +6560,7 @@
       <c r="A138" t="s">
         <v>47</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C138">
@@ -6592,7 +6598,7 @@
       <c r="A139" t="s">
         <v>47</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C139">
@@ -6630,7 +6636,7 @@
       <c r="A140" t="s">
         <v>47</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C140">
@@ -6668,7 +6674,7 @@
       <c r="A141" t="s">
         <v>47</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C141">
@@ -6706,7 +6712,7 @@
       <c r="A142" t="s">
         <v>49</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C142">
@@ -6744,7 +6750,7 @@
       <c r="A143" t="s">
         <v>49</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C143">
@@ -6782,7 +6788,7 @@
       <c r="A144" t="s">
         <v>49</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C144">
@@ -6820,7 +6826,7 @@
       <c r="A145" t="s">
         <v>49</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C145">
@@ -6858,7 +6864,7 @@
       <c r="A146" t="s">
         <v>49</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C146">
@@ -6896,7 +6902,7 @@
       <c r="A147" t="s">
         <v>49</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C147">
@@ -6934,7 +6940,7 @@
       <c r="A148" t="s">
         <v>49</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C148">
@@ -6972,7 +6978,7 @@
       <c r="A149" t="s">
         <v>49</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C149">
@@ -7010,7 +7016,7 @@
       <c r="A150" t="s">
         <v>51</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C150">
@@ -7048,7 +7054,7 @@
       <c r="A151" t="s">
         <v>51</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C151">
@@ -7086,7 +7092,7 @@
       <c r="A152" t="s">
         <v>51</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C152">
@@ -7124,7 +7130,7 @@
       <c r="A153" t="s">
         <v>51</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C153">
@@ -7162,7 +7168,7 @@
       <c r="A154" t="s">
         <v>51</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C154">
@@ -7200,7 +7206,7 @@
       <c r="A155" t="s">
         <v>51</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C155">
@@ -7238,7 +7244,7 @@
       <c r="A156" t="s">
         <v>51</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C156">
@@ -7276,7 +7282,7 @@
       <c r="A157" t="s">
         <v>51</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C157">
@@ -7314,7 +7320,7 @@
       <c r="A158" t="s">
         <v>53</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C158">
@@ -7352,7 +7358,7 @@
       <c r="A159" t="s">
         <v>53</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C159">
@@ -7390,7 +7396,7 @@
       <c r="A160" t="s">
         <v>53</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C160">
@@ -7428,7 +7434,7 @@
       <c r="A161" t="s">
         <v>53</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C161">
@@ -7466,7 +7472,7 @@
       <c r="A162" t="s">
         <v>53</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C162">
@@ -7504,7 +7510,7 @@
       <c r="A163" t="s">
         <v>53</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C163">
@@ -7542,7 +7548,7 @@
       <c r="A164" t="s">
         <v>53</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C164">
@@ -7580,7 +7586,7 @@
       <c r="A165" t="s">
         <v>53</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C165">
@@ -7618,7 +7624,7 @@
       <c r="A166" t="s">
         <v>55</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C166">
@@ -7656,7 +7662,7 @@
       <c r="A167" t="s">
         <v>55</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C167">
@@ -7694,7 +7700,7 @@
       <c r="A168" t="s">
         <v>55</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C168">
@@ -7732,7 +7738,7 @@
       <c r="A169" t="s">
         <v>55</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C169">
@@ -7770,7 +7776,7 @@
       <c r="A170" t="s">
         <v>55</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C170">
@@ -7808,7 +7814,7 @@
       <c r="A171" t="s">
         <v>55</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C171">
@@ -7846,7 +7852,7 @@
       <c r="A172" t="s">
         <v>55</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C172">
@@ -7884,7 +7890,7 @@
       <c r="A173" t="s">
         <v>55</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C173">
@@ -7922,7 +7928,7 @@
       <c r="A174" t="s">
         <v>57</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C174">
@@ -7960,7 +7966,7 @@
       <c r="A175" t="s">
         <v>57</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C175">
@@ -7998,7 +8004,7 @@
       <c r="A176" t="s">
         <v>57</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C176">
@@ -8036,7 +8042,7 @@
       <c r="A177" t="s">
         <v>57</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C177">
@@ -8074,7 +8080,7 @@
       <c r="A178" t="s">
         <v>59</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C178">
@@ -8112,7 +8118,7 @@
       <c r="A179" t="s">
         <v>59</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C179">
@@ -8150,7 +8156,7 @@
       <c r="A180" t="s">
         <v>59</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C180">
@@ -8188,7 +8194,7 @@
       <c r="A181" t="s">
         <v>59</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C181">
@@ -8226,7 +8232,7 @@
       <c r="A182" t="s">
         <v>59</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C182">
@@ -8264,7 +8270,7 @@
       <c r="A183" t="s">
         <v>59</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C183">
@@ -8302,7 +8308,7 @@
       <c r="A184" t="s">
         <v>59</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C184">
@@ -8340,7 +8346,7 @@
       <c r="A185" t="s">
         <v>59</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C185">
@@ -8378,7 +8384,7 @@
       <c r="A186" t="s">
         <v>61</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C186">
@@ -8416,7 +8422,7 @@
       <c r="A187" t="s">
         <v>61</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C187">
@@ -8454,7 +8460,7 @@
       <c r="A188" t="s">
         <v>61</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C188">
@@ -8492,7 +8498,7 @@
       <c r="A189" t="s">
         <v>61</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C189">
@@ -8530,7 +8536,7 @@
       <c r="A190" t="s">
         <v>61</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C190">
@@ -8568,7 +8574,7 @@
       <c r="A191" t="s">
         <v>61</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C191">
@@ -8606,7 +8612,7 @@
       <c r="A192" t="s">
         <v>61</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C192">
@@ -8644,7 +8650,7 @@
       <c r="A193" t="s">
         <v>61</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C193">
@@ -8682,7 +8688,7 @@
       <c r="A194" t="s">
         <v>63</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C194">
@@ -8720,7 +8726,7 @@
       <c r="A195" t="s">
         <v>63</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C195">
@@ -8758,7 +8764,7 @@
       <c r="A196" t="s">
         <v>63</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C196">
@@ -8796,7 +8802,7 @@
       <c r="A197" t="s">
         <v>63</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C197">
@@ -8834,7 +8840,7 @@
       <c r="A198" t="s">
         <v>63</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C198">
@@ -8872,7 +8878,7 @@
       <c r="A199" t="s">
         <v>63</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C199">
@@ -8910,7 +8916,7 @@
       <c r="A200" t="s">
         <v>63</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C200">
@@ -8948,7 +8954,7 @@
       <c r="A201" t="s">
         <v>63</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C201">
@@ -8986,7 +8992,7 @@
       <c r="A202" t="s">
         <v>65</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C202">
@@ -9024,7 +9030,7 @@
       <c r="A203" t="s">
         <v>65</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C203">
@@ -9062,7 +9068,7 @@
       <c r="A204" t="s">
         <v>65</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C204">
@@ -9100,7 +9106,7 @@
       <c r="A205" t="s">
         <v>65</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C205">
@@ -9138,7 +9144,7 @@
       <c r="A206" t="s">
         <v>65</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C206">
@@ -9176,7 +9182,7 @@
       <c r="A207" t="s">
         <v>65</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C207">
@@ -9214,7 +9220,7 @@
       <c r="A208" t="s">
         <v>65</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C208">
@@ -9252,7 +9258,7 @@
       <c r="A209" t="s">
         <v>67</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C209">
@@ -9290,7 +9296,7 @@
       <c r="A210" t="s">
         <v>67</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C210">
@@ -9328,7 +9334,7 @@
       <c r="A211" t="s">
         <v>67</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C211">
@@ -9366,7 +9372,7 @@
       <c r="A212" t="s">
         <v>67</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C212">
@@ -9404,7 +9410,7 @@
       <c r="A213" t="s">
         <v>67</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C213">
@@ -9442,7 +9448,7 @@
       <c r="A214" t="s">
         <v>67</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C214">
@@ -9480,7 +9486,7 @@
       <c r="A215" t="s">
         <v>67</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C215">
@@ -9518,7 +9524,7 @@
       <c r="A216" t="s">
         <v>67</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C216">
@@ -9556,7 +9562,7 @@
       <c r="A217" t="s">
         <v>69</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C217">
@@ -9594,7 +9600,7 @@
       <c r="A218" t="s">
         <v>69</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C218">
@@ -9632,7 +9638,7 @@
       <c r="A219" t="s">
         <v>69</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C219">
@@ -9670,7 +9676,7 @@
       <c r="A220" t="s">
         <v>69</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C220">
@@ -9708,7 +9714,7 @@
       <c r="A221" t="s">
         <v>69</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C221">
@@ -9746,7 +9752,7 @@
       <c r="A222" t="s">
         <v>69</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C222">
@@ -9784,7 +9790,7 @@
       <c r="A223" t="s">
         <v>69</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C223">
@@ -9822,7 +9828,7 @@
       <c r="A224" t="s">
         <v>69</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C224">
@@ -9860,7 +9866,7 @@
       <c r="A225" t="s">
         <v>71</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C225">
@@ -9898,7 +9904,7 @@
       <c r="A226" t="s">
         <v>71</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C226">
@@ -9936,7 +9942,7 @@
       <c r="A227" t="s">
         <v>71</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C227">
@@ -9974,7 +9980,7 @@
       <c r="A228" t="s">
         <v>71</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C228">
@@ -10012,7 +10018,7 @@
       <c r="A229" t="s">
         <v>71</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C229">
@@ -10050,7 +10056,7 @@
       <c r="A230" t="s">
         <v>71</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C230">
@@ -10088,7 +10094,7 @@
       <c r="A231" t="s">
         <v>71</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C231">
@@ -10126,7 +10132,7 @@
       <c r="A232" t="s">
         <v>71</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C232">
@@ -10164,7 +10170,7 @@
       <c r="A233" t="s">
         <v>73</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C233">
@@ -10202,7 +10208,7 @@
       <c r="A234" t="s">
         <v>73</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C234">
@@ -10240,7 +10246,7 @@
       <c r="A235" t="s">
         <v>73</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C235">
@@ -10278,7 +10284,7 @@
       <c r="A236" t="s">
         <v>73</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C236">
@@ -10316,7 +10322,7 @@
       <c r="A237" t="s">
         <v>73</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C237">
@@ -10354,7 +10360,7 @@
       <c r="A238" t="s">
         <v>73</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C238">
@@ -10392,7 +10398,7 @@
       <c r="A239" t="s">
         <v>73</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C239">
@@ -10430,7 +10436,7 @@
       <c r="A240" t="s">
         <v>73</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C240">
@@ -10468,7 +10474,7 @@
       <c r="A241" t="s">
         <v>75</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C241">
@@ -10506,7 +10512,7 @@
       <c r="A242" t="s">
         <v>75</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C242">
@@ -10544,7 +10550,7 @@
       <c r="A243" t="s">
         <v>75</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C243">
@@ -10582,7 +10588,7 @@
       <c r="A244" t="s">
         <v>75</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C244">
@@ -10620,7 +10626,7 @@
       <c r="A245" t="s">
         <v>75</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C245">
@@ -10658,7 +10664,7 @@
       <c r="A246" t="s">
         <v>75</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C246">
@@ -10696,7 +10702,7 @@
       <c r="A247" t="s">
         <v>75</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C247">
@@ -10734,7 +10740,7 @@
       <c r="A248" t="s">
         <v>75</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C248">
@@ -10772,7 +10778,7 @@
       <c r="A249" t="s">
         <v>77</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C249">
@@ -10810,7 +10816,7 @@
       <c r="A250" t="s">
         <v>77</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C250">
@@ -10848,7 +10854,7 @@
       <c r="A251" t="s">
         <v>77</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C251">
@@ -10886,7 +10892,7 @@
       <c r="A252" t="s">
         <v>77</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C252">
@@ -10924,7 +10930,7 @@
       <c r="A253" t="s">
         <v>77</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C253">
@@ -10962,7 +10968,7 @@
       <c r="A254" t="s">
         <v>77</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C254">
@@ -11000,7 +11006,7 @@
       <c r="A255" t="s">
         <v>77</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C255">
@@ -11038,7 +11044,7 @@
       <c r="A256" t="s">
         <v>77</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C256">
@@ -11076,7 +11082,7 @@
       <c r="A257" t="s">
         <v>79</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C257">
@@ -11114,7 +11120,7 @@
       <c r="A258" t="s">
         <v>79</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C258">
@@ -11152,7 +11158,7 @@
       <c r="A259" t="s">
         <v>79</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C259">
@@ -11190,7 +11196,7 @@
       <c r="A260" t="s">
         <v>79</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C260">
@@ -11228,7 +11234,7 @@
       <c r="A261" t="s">
         <v>79</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C261">
@@ -11266,7 +11272,7 @@
       <c r="A262" t="s">
         <v>79</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C262">
@@ -11304,7 +11310,7 @@
       <c r="A263" t="s">
         <v>81</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C263">
@@ -11342,7 +11348,7 @@
       <c r="A264" t="s">
         <v>81</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C264">
@@ -11380,7 +11386,7 @@
       <c r="A265" t="s">
         <v>81</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C265">
@@ -11418,7 +11424,7 @@
       <c r="A266" t="s">
         <v>81</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C266">
@@ -11456,7 +11462,7 @@
       <c r="A267" t="s">
         <v>81</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C267">
@@ -11494,7 +11500,7 @@
       <c r="A268" t="s">
         <v>81</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C268">
@@ -11532,7 +11538,7 @@
       <c r="A269" t="s">
         <v>81</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C269">
@@ -11570,7 +11576,7 @@
       <c r="A270" t="s">
         <v>81</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C270">
